--- a/DC-Colos.xlsx
+++ b/DC-Colos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H344"/>
+  <dimension ref="A1:H343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8599,12 +8599,12 @@
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>KJA</t>
+          <t>KUL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Krasnoyarsk, Russia</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8614,107 +8614,103 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Krasnoyarsk</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>56.172901</v>
+        <v>2.74558</v>
       </c>
       <c r="H217" t="n">
-        <v>92.493301</v>
+        <v>101.709999</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>KUL</t>
+          <t>PKX</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Langfang, China</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Langfang</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="G218" t="n">
-        <v>2.74558</v>
-      </c>
-      <c r="H218" t="n">
-        <v>101.709999</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>PKX</t>
+          <t>MFM</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Langfang, China</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Langfang</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
+          <t>Taipa</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>22.149599</v>
+      </c>
+      <c r="H219" t="n">
+        <v>113.592003</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>MFM</t>
+          <t>MLE</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Malé, Maldives</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8724,31 +8720,35 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Taipa</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr"/>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MV</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>22.149599</v>
+        <v>4.19183</v>
       </c>
       <c r="H220" t="n">
-        <v>113.592003</v>
+        <v>73.529099</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>MLE</t>
+          <t>MNL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Malé, Maldives</t>
+          <t>Manila, Philippines</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8758,35 +8758,35 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>MV</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>4.19183</v>
+        <v>14.5086</v>
       </c>
       <c r="H221" t="n">
-        <v>73.529099</v>
+        <v>121.019997</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>MNL</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Manila, Philippines</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8796,35 +8796,35 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>14.5086</v>
+        <v>19.088699</v>
       </c>
       <c r="H222" t="n">
-        <v>121.019997</v>
+        <v>72.867897</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>NAG</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Nagpur, India</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Naqpur</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -8848,21 +8848,21 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>19.088699</v>
+        <v>21.092199</v>
       </c>
       <c r="H223" t="n">
-        <v>72.867897</v>
+        <v>79.047203</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>NAG</t>
+          <t>OKA</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Nagpur, India</t>
+          <t>Naha, Japan</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8872,35 +8872,35 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Naqpur</t>
+          <t>Naha</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>21.092199</v>
+        <v>26.195801</v>
       </c>
       <c r="H224" t="n">
-        <v>79.047203</v>
+        <v>127.646004</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>OKA</t>
+          <t>DEL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Naha, Japan</t>
+          <t>New Delhi, India</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8910,35 +8910,35 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Naha</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>26.195801</v>
+        <v>28.5665</v>
       </c>
       <c r="H225" t="n">
-        <v>127.646004</v>
+        <v>77.103104</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>DEL</t>
+          <t>KIX</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>New Delhi, India</t>
+          <t>Osaka, Japan</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8948,35 +8948,35 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Osaka</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>28.5665</v>
+        <v>34.427299</v>
       </c>
       <c r="H226" t="n">
-        <v>77.103104</v>
+        <v>135.244003</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>KIX</t>
+          <t>PAT</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Osaka, Japan</t>
+          <t>Patna, India</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8986,35 +8986,35 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Osaka</t>
+          <t>Patna</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>34.427299</v>
+        <v>25.591299</v>
       </c>
       <c r="H227" t="n">
-        <v>135.244003</v>
+        <v>85.087997</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>PAT</t>
+          <t>PNH</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Patna, India</t>
+          <t>Phnom Penh, Cambodia</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -9024,179 +9024,179 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KH</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>25.591299</v>
+        <v>11.5466</v>
       </c>
       <c r="H228" t="n">
-        <v>85.087997</v>
+        <v>104.844002</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>PNH</t>
+          <t>TAO</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Phnom Penh, Cambodia</t>
+          <t>Qingdao, China</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>KH</t>
-        </is>
-      </c>
-      <c r="G229" t="n">
-        <v>11.5466</v>
-      </c>
-      <c r="H229" t="n">
-        <v>104.844002</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>TAO</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Qingdao, China</t>
+          <t>Seoul, South Korea</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>37.469101</v>
+      </c>
+      <c r="H230" t="n">
+        <v>126.450996</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Seoul, South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G231" t="n">
-        <v>37.469101</v>
-      </c>
-      <c r="H231" t="n">
-        <v>126.450996</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>SIN</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>1.35019</v>
+      </c>
+      <c r="H232" t="n">
+        <v>103.994003</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>SIN</t>
+          <t>URT</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Surat Thani, Thailand</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -9206,35 +9206,35 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Surat Thani</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1.35019</v>
+        <v>9.1326</v>
       </c>
       <c r="H233" t="n">
-        <v>103.994003</v>
+        <v>99.135597</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>URT</t>
+          <t>TPE</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Surat Thani, Thailand</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9244,35 +9244,31 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Surat Thani</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>9.1326</v>
+        <v>25.0777</v>
       </c>
       <c r="H234" t="n">
-        <v>99.135597</v>
+        <v>121.233002</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>TPE</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -9282,31 +9278,35 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Taipei</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>25.0777</v>
+        <v>35.764702</v>
       </c>
       <c r="H235" t="n">
-        <v>121.233002</v>
+        <v>140.386002</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>ULN</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>Ulaanbaatar, Mongolia</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -9316,35 +9316,35 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Ulan Bator</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>35.764702</v>
+        <v>47.843102</v>
       </c>
       <c r="H236" t="n">
-        <v>140.386002</v>
+        <v>106.766998</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>ULN</t>
+          <t>VTE</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Ulaanbaatar, Mongolia</t>
+          <t>Vientiane, Laos</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -9354,145 +9354,145 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Ulan Bator</t>
+          <t>Vientiane</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>47.843102</v>
+        <v>17.9883</v>
       </c>
       <c r="H237" t="n">
-        <v>106.766998</v>
+        <v>102.563004</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>VTE</t>
+          <t>KHN</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Vientiane, Laos</t>
+          <t>Xinyu, China</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Vientiane</t>
+          <t>Xinyu</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="G238" t="n">
-        <v>17.9883</v>
-      </c>
-      <c r="H238" t="n">
-        <v>102.563004</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>KHN</t>
+          <t>EVN</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Xinyu, China</t>
+          <t>Yerevan, Armenia</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Xinyu</t>
+          <t>Yerevan</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>40.147301</v>
+      </c>
+      <c r="H239" t="n">
+        <v>44.395901</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>EVN</t>
+          <t>JOG</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Yerevan, Armenia</t>
+          <t>Yogyakarta, Indonesia</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Yerevan</t>
+          <t>Yogyakarta-Java Island</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>40.147301</v>
+        <v>-7.78818</v>
       </c>
       <c r="H240" t="n">
-        <v>44.395901</v>
+        <v>110.431999</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>JOG</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Yogyakarta, Indonesia</t>
+          <t>Cagayan de Oro, Philippines</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9502,35 +9502,35 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Yogyakarta-Java Island</t>
+          <t>Cagayan De Oro City</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>-7.78818</v>
+        <v>8.415620000000001</v>
       </c>
       <c r="H241" t="n">
-        <v>110.431999</v>
+        <v>124.611</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>COK</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Cagayan de Oro, Philippines</t>
+          <t>Kochi, India</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9540,35 +9540,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Cagayan De Oro City</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>8.415620000000001</v>
+        <v>10.152</v>
       </c>
       <c r="H242" t="n">
-        <v>124.611</v>
+        <v>76.401901</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>COK</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Kochi, India</t>
+          <t>Denpasar, Indonesia</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9578,35 +9578,35 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Cochin</t>
+          <t>Denpasar-Bali Island</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>10.152</v>
+        <v>-8.74817</v>
       </c>
       <c r="H243" t="n">
-        <v>76.401901</v>
+        <v>115.167</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Denpasar, Indonesia</t>
+          <t>Kannur, India</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9616,73 +9616,69 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Denpasar-Bali Island</t>
+          <t>Mattanur</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>-8.74817</v>
+        <v>11.92</v>
       </c>
       <c r="H244" t="n">
-        <v>115.167</v>
+        <v>75.55</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>SZX</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Kannur, India</t>
+          <t>Shenzhen, China</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Mattanur</t>
+          <t>Shenzhen</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G245" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="H245" t="n">
-        <v>75.55</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>SZX</t>
+          <t>KWE</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Shenzhen, China</t>
+          <t>Guiyang, China</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9692,7 +9688,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Guiyang</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -9711,12 +9707,12 @@
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>KWE</t>
+          <t>HGH</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Guiyang, China</t>
+          <t>Shaoxing, China</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9726,7 +9722,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Guiyang</t>
+          <t>Shaoxing</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -9745,12 +9741,12 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>HGH</t>
+          <t>CZX</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Shaoxing, China</t>
+          <t>Changzhou, China</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9760,7 +9756,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Shaoxing</t>
+          <t>Changzhou</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -9779,12 +9775,12 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>CZX</t>
+          <t>KMG</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Changzhou, China</t>
+          <t>Kunming, China</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9794,7 +9790,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Changzhou</t>
+          <t>Kunming</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -9813,84 +9809,84 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>KMG</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Kunming, China</t>
+          <t>Chiang Mai, Thailand</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Kunming</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>18.7668</v>
+      </c>
+      <c r="H250" t="n">
+        <v>98.96260100000001</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>CGO</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Chiang Mai, Thailand</t>
+          <t>Zhengzhou, China</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Zhengzhou</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>TH</t>
-        </is>
-      </c>
-      <c r="G251" t="n">
-        <v>18.7668</v>
-      </c>
-      <c r="H251" t="n">
-        <v>98.96260100000001</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>CGO</t>
+          <t>TYN</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Zhengzhou, China</t>
+          <t>Yangquan, China</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9900,7 +9896,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Zhengzhou</t>
+          <t>Yangquan</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -9919,12 +9915,12 @@
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>TYN</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Yangquan, China</t>
+          <t>Changsha, China</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9934,7 +9930,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Yangquan</t>
+          <t>Changsha</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -9953,12 +9949,12 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>DLC</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Changsha, China</t>
+          <t>Dalian, China</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9968,7 +9964,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Changsha</t>
+          <t>Dalian</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -9987,12 +9983,12 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>DLC</t>
+          <t>CKG</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Dalian, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -10002,7 +9998,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Dalian</t>
+          <t>Chongqing</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -10021,12 +10017,12 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>CKG</t>
+          <t>XFN</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Xiangyang, China</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -10036,7 +10032,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Chongqing</t>
+          <t>Xiangyang</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -10055,118 +10051,122 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>XFN</t>
+          <t>DAD</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Xiangyang, China</t>
+          <t>Da Nang, Vietnam</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Xiangyang</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>16.0439</v>
+      </c>
+      <c r="H257" t="n">
+        <v>108.198997</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>DAD</t>
+          <t>JXG</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Da Nang, Vietnam</t>
+          <t>Jiaxing, China</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Jiaxing</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>VN</t>
-        </is>
-      </c>
-      <c r="G258" t="n">
-        <v>16.0439</v>
-      </c>
-      <c r="H258" t="n">
-        <v>108.198997</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>JXG</t>
+          <t>CRK</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Jiaxing, China</t>
+          <t>Tarlac City, Philippines</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Jiaxing</t>
+          <t>Mabalacat</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>15.186</v>
+      </c>
+      <c r="H259" t="n">
+        <v>120.559998</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>CRK</t>
+          <t>PBH</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Tarlac City, Philippines</t>
+          <t>Thimphu, Bhutan</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -10176,183 +10176,179 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Mabalacat</t>
+          <t>Paro</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BT</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>15.186</v>
+        <v>27.4032</v>
       </c>
       <c r="H260" t="n">
-        <v>120.559998</v>
+        <v>89.424599</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>PBH</t>
+          <t>XIY</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Thimphu, Bhutan</t>
+          <t>Baoji, China</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Paro</t>
+          <t>Baoji</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="G261" t="n">
-        <v>27.4032</v>
-      </c>
-      <c r="H261" t="n">
-        <v>89.424599</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>XIY</t>
+          <t>KCH</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Baoji, China</t>
+          <t>Kuching, Malaysia</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Baoji</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>1.4847</v>
+      </c>
+      <c r="H262" t="n">
+        <v>110.347</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>KCH</t>
+          <t>AKX</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Kuching, Malaysia</t>
+          <t>Aktobe, Kazakhstan</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>Aktyubinsk</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="G263" t="n">
-        <v>1.4847</v>
+        <v>50.2458</v>
       </c>
       <c r="H263" t="n">
-        <v>110.347</v>
+        <v>57.206699</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>AKX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Aktobe, Kazakhstan</t>
+          <t>Tongren, China</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Aktyubinsk</t>
+          <t>Tongren</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="G264" t="n">
-        <v>50.2458</v>
-      </c>
-      <c r="H264" t="n">
-        <v>57.206699</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Tongren, China</t>
+          <t>Taizhou, China</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10362,7 +10358,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Tongren</t>
+          <t>Taizhou</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -10381,46 +10377,50 @@
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Taizhou, China</t>
+          <t>Bishkek, Kyrgyzstan</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Taizhou</t>
+          <t>Bishkek</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>43.061272</v>
+      </c>
+      <c r="H266" t="n">
+        <v>74.477508</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>FRU</t>
+          <t>MLG</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Bishkek, Kyrgyzstan</t>
+          <t>Malang, Indonesia</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10430,35 +10430,35 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Bishkek</t>
+          <t>Malang-Java Island</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>43.061272</v>
+        <v>-7.92656</v>
       </c>
       <c r="H267" t="n">
-        <v>74.477508</v>
+        <v>112.714996</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>MLG</t>
+          <t>LHE</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Malang, Indonesia</t>
+          <t>Lahore, Pakistan</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10468,107 +10468,103 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Malang-Java Island</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>-7.92656</v>
+        <v>31.521601</v>
       </c>
       <c r="H268" t="n">
-        <v>112.714996</v>
+        <v>74.403603</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>LHE</t>
+          <t>CTU</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Lahore, Pakistan</t>
+          <t>Chengdu, China</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Chengdu</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G269" t="n">
-        <v>31.521601</v>
-      </c>
-      <c r="H269" t="n">
-        <v>74.403603</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>CTU</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Chengdu, China</t>
+          <t>Agra, India</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>Chengdu</t>
-        </is>
-      </c>
+          <t>Asia Pacific</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>27.1558</v>
+      </c>
+      <c r="H270" t="n">
+        <v>77.960899</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>AGR</t>
+          <t>CJB</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Agra, India</t>
+          <t>Coimbatore, India</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -10576,7 +10572,11 @@
           <t>Asia Pacific</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>India</t>
@@ -10588,165 +10588,165 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>27.1558</v>
+        <v>11.03</v>
       </c>
       <c r="H271" t="n">
-        <v>77.960899</v>
+        <v>77.043404</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>CJB</t>
+          <t>ACX</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Xingyi, China</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Xingyi</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G272" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="H272" t="n">
-        <v>77.043404</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>ACX</t>
+          <t>BBI</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Xingyi, China</t>
+          <t>Bhubaneswar, India</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Xingyi</t>
+          <t>Bhubaneswar</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>20.2444</v>
+      </c>
+      <c r="H273" t="n">
+        <v>85.817802</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>BBI</t>
+          <t>LYA</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Bhubaneswar, India</t>
+          <t>Luoyang, China</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Bhubaneswar</t>
+          <t>Luoyang</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G274" t="n">
-        <v>20.2444</v>
-      </c>
-      <c r="H274" t="n">
-        <v>85.817802</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>LYA</t>
+          <t>PNQ</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Luoyang, China</t>
+          <t>Pune, India</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Luoyang</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>18.5821</v>
+      </c>
+      <c r="H275" t="n">
+        <v>73.919701</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>PNQ</t>
+          <t>JRG</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Pune, India</t>
+          <t>Sambalpur, India</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Jharsuguda</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -10770,93 +10770,93 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>18.5821</v>
+        <v>21.9135</v>
       </c>
       <c r="H276" t="n">
-        <v>73.919701</v>
+        <v>84.0504</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>JRG</t>
+          <t>AVA</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Sambalpur, India</t>
+          <t>Anshun, China</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Jharsuguda</t>
+          <t>Anshun</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G277" t="n">
-        <v>21.9135</v>
-      </c>
-      <c r="H277" t="n">
-        <v>84.0504</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>AVA</t>
+          <t>NQZ</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Anshun, China</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Anshun</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>51.022202</v>
+      </c>
+      <c r="H278" t="n">
+        <v>71.466904</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>NQZ</t>
+          <t>BDQ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Jamnagar, India</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10866,35 +10866,35 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Vadodara</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>51.022202</v>
+        <v>22.336201</v>
       </c>
       <c r="H279" t="n">
-        <v>71.466904</v>
+        <v>73.226303</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>BDQ</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Jamnagar, India</t>
+          <t>Udaipur, India</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -10918,21 +10918,21 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>22.336201</v>
+        <v>24.617701</v>
       </c>
       <c r="H280" t="n">
-        <v>73.226303</v>
+        <v>73.896103</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>AIP</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Udaipur, India</t>
+          <t>Jalandhar, India</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10940,11 +10940,7 @@
           <t>Asia Pacific</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>Udaipur</t>
-        </is>
-      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>India</t>
@@ -10956,89 +10952,93 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>24.617701</v>
+        <v>31.4338</v>
       </c>
       <c r="H281" t="n">
-        <v>73.896103</v>
+        <v>75.758797</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>AIP</t>
+          <t>LHW</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Jalandhar, India</t>
+          <t>Lanzhou, China</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Lanzhou</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="G282" t="n">
-        <v>31.4338</v>
-      </c>
-      <c r="H282" t="n">
-        <v>75.758797</v>
-      </c>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>LHW</t>
+          <t>DYU</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Lanzhou, China</t>
+          <t>Dushanbe, Tajikistan</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Asia Pacific</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Lanzhou</t>
+          <t>Dushanbe</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr"/>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>38.543301</v>
+      </c>
+      <c r="H283" t="n">
+        <v>68.824997</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>DYU</t>
+          <t>LUH</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dushanbe, Tajikistan</t>
+          <t>Ludhiana, India</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -11046,71 +11046,71 @@
           <t>Asia Pacific</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Dushanbe</t>
-        </is>
-      </c>
+      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G284" t="n">
-        <v>38.543301</v>
+        <v>30.8547</v>
       </c>
       <c r="H284" t="n">
-        <v>68.824997</v>
+        <v>75.95259900000001</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>LUH</t>
+          <t>ABQ</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Ludhiana, India</t>
+          <t>Albuquerque, NM, United States</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Asia Pacific</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Albuquerque</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>30.8547</v>
+        <v>35.040199</v>
       </c>
       <c r="H285" t="n">
-        <v>75.95259900000001</v>
+        <v>-106.609001</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>ABQ</t>
+          <t>ANC</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, United States</t>
+          <t>Anchorage, AK, United States</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Albuquerque</t>
+          <t>Anchorage</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -11134,21 +11134,21 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>35.040199</v>
+        <v>61.1744</v>
       </c>
       <c r="H286" t="n">
-        <v>-106.609001</v>
+        <v>-149.996002</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>ANC</t>
+          <t>IAD</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Anchorage, AK, United States</t>
+          <t>Ashburn, VA, United States</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Anchorage</t>
+          <t>Dulles</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -11172,21 +11172,21 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>61.1744</v>
+        <v>38.9445</v>
       </c>
       <c r="H287" t="n">
-        <v>-149.996002</v>
+        <v>-77.455803</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>IAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Ashburn, VA, United States</t>
+          <t>Atlanta, GA, United States</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Dulles</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -11210,21 +11210,21 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>38.9445</v>
+        <v>33.6367</v>
       </c>
       <c r="H288" t="n">
-        <v>-77.455803</v>
+        <v>-84.428101</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Atlanta, GA, United States</t>
+          <t>Austin, TX, United States</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -11248,21 +11248,21 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>33.6367</v>
+        <v>30.1945</v>
       </c>
       <c r="H289" t="n">
-        <v>-84.428101</v>
+        <v>-97.669899</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Austin, TX, United States</t>
+          <t>Bangor, ME, United States</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>30.1945</v>
+        <v>44.8074</v>
       </c>
       <c r="H290" t="n">
-        <v>-97.669899</v>
+        <v>-68.828102</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Bangor, ME, United States</t>
+          <t>Boston, MA, United States</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -11324,21 +11324,21 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>44.8074</v>
+        <v>42.3643</v>
       </c>
       <c r="H291" t="n">
-        <v>-68.828102</v>
+        <v>-71.00520299999999</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Boston, MA, United States</t>
+          <t>Buffalo, NY, United States</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Buffalo</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -11362,21 +11362,21 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>42.3643</v>
+        <v>42.940498</v>
       </c>
       <c r="H292" t="n">
-        <v>-71.00520299999999</v>
+        <v>-78.732201</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>YYC</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Buffalo, NY, United States</t>
+          <t>Calgary, AB, Canada</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -11386,35 +11386,35 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>Calgary</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G293" t="n">
-        <v>42.940498</v>
+        <v>51.113899</v>
       </c>
       <c r="H293" t="n">
-        <v>-78.732201</v>
+        <v>-114.019997</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>YYC</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Calgary, AB, Canada</t>
+          <t>Charlotte, NC, United States</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -11424,35 +11424,35 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Calgary</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G294" t="n">
-        <v>51.113899</v>
+        <v>35.214001</v>
       </c>
       <c r="H294" t="n">
-        <v>-114.019997</v>
+        <v>-80.9431</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Charlotte, NC, United States</t>
+          <t>Chicago, IL, United States</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -11476,21 +11476,21 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>35.214001</v>
+        <v>41.9786</v>
       </c>
       <c r="H295" t="n">
-        <v>-80.9431</v>
+        <v>-87.90479999999999</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>ORD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Chicago, IL, United States</t>
+          <t>Cleveland, OH, United States</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -11514,21 +11514,21 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>41.9786</v>
+        <v>41.411701</v>
       </c>
       <c r="H296" t="n">
-        <v>-87.90479999999999</v>
+        <v>-81.8498</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CMH</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Cleveland, OH, United States</t>
+          <t>Columbus, OH, United States</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -11552,21 +11552,21 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>41.411701</v>
+        <v>39.998001</v>
       </c>
       <c r="H297" t="n">
-        <v>-81.8498</v>
+        <v>-82.891899</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>CMH</t>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Columbus, OH, United States</t>
+          <t>Dallas, TX, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Dallas-Fort Worth</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -11590,21 +11590,21 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>39.998001</v>
+        <v>32.896801</v>
       </c>
       <c r="H298" t="n">
-        <v>-82.891899</v>
+        <v>-97.03800200000001</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>DFW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Dallas, TX, United States</t>
+          <t>Denver, CO, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -11628,21 +11628,21 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>32.896801</v>
+        <v>39.861698</v>
       </c>
       <c r="H299" t="n">
-        <v>-97.03800200000001</v>
+        <v>-104.672997</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Denver, CO, United States</t>
+          <t>Detroit, MI, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -11666,21 +11666,21 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>39.861698</v>
+        <v>42.212399</v>
       </c>
       <c r="H300" t="n">
-        <v>-104.672997</v>
+        <v>-83.35340100000001</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>DTW</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Detroit, MI, United States</t>
+          <t>Durham, NC, United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Raleigh/Durham</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -11704,21 +11704,21 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>42.212399</v>
+        <v>35.877602</v>
       </c>
       <c r="H301" t="n">
-        <v>-83.35340100000001</v>
+        <v>-78.787498</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>GDL</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Durham, NC, United States</t>
+          <t>Guadalajara, Mexico</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -11728,35 +11728,35 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Raleigh/Durham</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G302" t="n">
-        <v>35.877602</v>
+        <v>20.521799</v>
       </c>
       <c r="H302" t="n">
-        <v>-78.787498</v>
+        <v>-103.310997</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>GDL</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Guadalajara, Mexico</t>
+          <t>Halifax, Canada</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11766,35 +11766,35 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>20.521799</v>
+        <v>44.880798</v>
       </c>
       <c r="H303" t="n">
-        <v>-103.310997</v>
+        <v>-63.508598</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Halifax, Canada</t>
+          <t>Honolulu, HI, United States</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11804,35 +11804,35 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Honolulu</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G304" t="n">
-        <v>44.880798</v>
+        <v>21.318701</v>
       </c>
       <c r="H304" t="n">
-        <v>-63.508598</v>
+        <v>-157.921997</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>HNL</t>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Honolulu, HI, United States</t>
+          <t>Houston, TX, United States</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Honolulu</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -11856,21 +11856,21 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>21.318701</v>
+        <v>29.9844</v>
       </c>
       <c r="H305" t="n">
-        <v>-157.921997</v>
+        <v>-95.34139999999999</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>IAH</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Houston, TX, United States</t>
+          <t>Indianapolis, IN, United States</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -11894,21 +11894,21 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>29.9844</v>
+        <v>39.7173</v>
       </c>
       <c r="H306" t="n">
-        <v>-95.34139999999999</v>
+        <v>-86.294403</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, United States</t>
+          <t>Jacksonville, FL, United States</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -11932,21 +11932,21 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>39.7173</v>
+        <v>30.494101</v>
       </c>
       <c r="H307" t="n">
-        <v>-86.294403</v>
+        <v>-81.68789700000001</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, United States</t>
+          <t>Kansas City, MO, United States</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -11970,21 +11970,21 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>30.494101</v>
+        <v>39.2976</v>
       </c>
       <c r="H308" t="n">
-        <v>-81.68789700000001</v>
+        <v>-94.713898</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>KIN</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Kansas City, MO, United States</t>
+          <t>Kingston, Jamaica</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11994,35 +11994,35 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>39.2976</v>
+        <v>17.935699</v>
       </c>
       <c r="H309" t="n">
-        <v>-94.713898</v>
+        <v>-76.787498</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>KIN</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Kingston, Jamaica</t>
+          <t>Las Vegas, NV, United States</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -12032,35 +12032,35 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Las Vegas</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>JM</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>17.935699</v>
+        <v>36.080101</v>
       </c>
       <c r="H310" t="n">
-        <v>-76.787498</v>
+        <v>-115.152</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>LAS</t>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, United States</t>
+          <t>Los Angeles, CA, United States</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -12084,21 +12084,21 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>36.080101</v>
+        <v>33.942501</v>
       </c>
       <c r="H311" t="n">
-        <v>-115.152</v>
+        <v>-118.407997</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, United States</t>
+          <t>Memphis, TN, United States</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -12122,21 +12122,21 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>33.942501</v>
+        <v>35.0424</v>
       </c>
       <c r="H312" t="n">
-        <v>-118.407997</v>
+        <v>-89.97669999999999</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Memphis, TN, United States</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -12146,35 +12146,35 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>35.0424</v>
+        <v>19.4363</v>
       </c>
       <c r="H313" t="n">
-        <v>-89.97669999999999</v>
+        <v>-99.072098</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>Miami, FL, United States</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -12184,35 +12184,35 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>19.4363</v>
+        <v>25.7932</v>
       </c>
       <c r="H314" t="n">
-        <v>-99.072098</v>
+        <v>-80.290604</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MSP</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Miami, FL, United States</t>
+          <t>Minneapolis, MN, United States</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -12236,21 +12236,21 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>25.7932</v>
+        <v>44.882</v>
       </c>
       <c r="H315" t="n">
-        <v>-80.290604</v>
+        <v>-93.221802</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>MSP</t>
+          <t>YUL</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, United States</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -12260,35 +12260,35 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>44.882</v>
+        <v>45.4706</v>
       </c>
       <c r="H316" t="n">
-        <v>-93.221802</v>
+        <v>-73.740799</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>YUL</t>
+          <t>BNA</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Nashville, United States</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -12298,35 +12298,35 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>45.4706</v>
+        <v>36.1245</v>
       </c>
       <c r="H317" t="n">
-        <v>-73.740799</v>
+        <v>-86.6782</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>BNA</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Nashville, United States</t>
+          <t>Newark, NJ, United States</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -12350,21 +12350,21 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>36.1245</v>
+        <v>40.692501</v>
       </c>
       <c r="H318" t="n">
-        <v>-86.6782</v>
+        <v>-74.168701</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>EWR</t>
+          <t>ORF</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Newark, NJ, United States</t>
+          <t>Norfolk, VA, United States</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -12388,21 +12388,21 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>40.692501</v>
+        <v>36.8946</v>
       </c>
       <c r="H319" t="n">
-        <v>-74.168701</v>
+        <v>-76.20120199999999</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>ORF</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Norfolk, VA, United States</t>
+          <t>Oklahoma City, OK, United States</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -12426,21 +12426,21 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>36.8946</v>
+        <v>35.393101</v>
       </c>
       <c r="H320" t="n">
-        <v>-76.20120199999999</v>
+        <v>-97.6007</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>OMA</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, United States</t>
+          <t>Omaha, NE, United States</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Omaha</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -12464,21 +12464,21 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>35.393101</v>
+        <v>41.3032</v>
       </c>
       <c r="H321" t="n">
-        <v>-97.6007</v>
+        <v>-95.894096</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>OMA</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Omaha, NE, United States</t>
+          <t>Philadelphia, United States</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Omaha</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -12502,21 +12502,21 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>41.3032</v>
+        <v>39.871899</v>
       </c>
       <c r="H322" t="n">
-        <v>-95.894096</v>
+        <v>-75.241096</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Philadelphia, United States</t>
+          <t>Phoenix, AZ, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -12540,21 +12540,21 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>39.871899</v>
+        <v>33.434299</v>
       </c>
       <c r="H323" t="n">
-        <v>-75.241096</v>
+        <v>-112.012001</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, United States</t>
+          <t>Pittsburgh, PA, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -12578,21 +12578,21 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>33.434299</v>
+        <v>40.491501</v>
       </c>
       <c r="H324" t="n">
-        <v>-112.012001</v>
+        <v>-80.23290299999999</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PDX</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, United States</t>
+          <t>Portland, OR, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -12616,21 +12616,21 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>40.491501</v>
+        <v>45.588699</v>
       </c>
       <c r="H325" t="n">
-        <v>-80.23290299999999</v>
+        <v>-122.598</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>PDX</t>
+          <t>QRO</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Portland, OR, United States</t>
+          <t>Queretaro, MX, Mexico</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -12640,35 +12640,35 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>45.588699</v>
+        <v>20.6173</v>
       </c>
       <c r="H326" t="n">
-        <v>-122.598</v>
+        <v>-100.185997</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>QRO</t>
+          <t>RIC</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Queretaro, MX, Mexico</t>
+          <t>Richmond, VA, United States</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -12678,35 +12678,35 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>20.6173</v>
+        <v>37.505199</v>
       </c>
       <c r="H327" t="n">
-        <v>-100.185997</v>
+        <v>-77.31970200000001</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>RIC</t>
+          <t>SMF</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Richmond, VA, United States</t>
+          <t>Sacramento, CA, United States</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -12730,21 +12730,21 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>37.505199</v>
+        <v>38.6954</v>
       </c>
       <c r="H328" t="n">
-        <v>-77.31970200000001</v>
+        <v>-121.591003</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>SMF</t>
+          <t>SLC</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Sacramento, CA, United States</t>
+          <t>Salt Lake City, UT, United States</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -12768,21 +12768,21 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>38.6954</v>
+        <v>40.788399</v>
       </c>
       <c r="H329" t="n">
-        <v>-121.591003</v>
+        <v>-111.977997</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>SLC</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, United States</t>
+          <t>San Antonio, TX, United States</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -12806,21 +12806,21 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>40.788399</v>
+        <v>29.533701</v>
       </c>
       <c r="H330" t="n">
-        <v>-111.977997</v>
+        <v>-98.469803</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>San Antonio, TX, United States</t>
+          <t>San Diego, CA, United States</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -12844,21 +12844,21 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>29.533701</v>
+        <v>32.733601</v>
       </c>
       <c r="H331" t="n">
-        <v>-98.469803</v>
+        <v>-117.190002</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>San Diego, CA, United States</t>
+          <t>San Francisco, CA, United States</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -12882,21 +12882,21 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>32.733601</v>
+        <v>37.618999</v>
       </c>
       <c r="H332" t="n">
-        <v>-117.190002</v>
+        <v>-122.375</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Jose, CA, United States</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -12920,21 +12920,21 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>37.618999</v>
+        <v>37.362598</v>
       </c>
       <c r="H333" t="n">
-        <v>-122.375</v>
+        <v>-121.929001</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>YXE</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>San Jose, CA, United States</t>
+          <t>Saskatoon, SK, Canada</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -12944,35 +12944,35 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Saskatoon</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>37.362598</v>
+        <v>52.170799</v>
       </c>
       <c r="H334" t="n">
-        <v>-121.929001</v>
+        <v>-106.699997</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>YXE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Saskatoon, SK, Canada</t>
+          <t>Seattle, WA, United States</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -12982,35 +12982,35 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Saskatoon</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>52.170799</v>
+        <v>47.449001</v>
       </c>
       <c r="H335" t="n">
-        <v>-106.699997</v>
+        <v>-122.308998</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Seattle, WA, United States</t>
+          <t>Sioux Falls, SD, United States</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Sioux Falls</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -13034,21 +13034,21 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>47.449001</v>
+        <v>43.582001</v>
       </c>
       <c r="H336" t="n">
-        <v>-122.308998</v>
+        <v>-96.74189800000001</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>FSD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, United States</t>
+          <t>St. Louis, MO, United States</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Sioux Falls</t>
+          <t>St Louis</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -13072,21 +13072,21 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>43.582001</v>
+        <v>38.748699</v>
       </c>
       <c r="H337" t="n">
-        <v>-96.74189800000001</v>
+        <v>-90.370003</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>St. Louis, MO, United States</t>
+          <t>Tallahassee, FL, United States</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>St Louis</t>
+          <t>Tallahassee</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -13110,21 +13110,21 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>38.748699</v>
+        <v>30.3965</v>
       </c>
       <c r="H338" t="n">
-        <v>-90.370003</v>
+        <v>-84.35030399999999</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, United States</t>
+          <t>Tampa, FL, United States</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Tallahassee</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -13148,21 +13148,21 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>30.3965</v>
+        <v>27.9755</v>
       </c>
       <c r="H339" t="n">
-        <v>-84.35030399999999</v>
+        <v>-82.533203</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>YYZ</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Tampa, FL, United States</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -13172,35 +13172,35 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Tampa</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G340" t="n">
-        <v>27.9755</v>
+        <v>43.6772</v>
       </c>
       <c r="H340" t="n">
-        <v>-82.533203</v>
+        <v>-79.6306</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>YYZ</t>
+          <t>YVR</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Vancouver, BC, Canada</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -13210,7 +13210,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -13224,21 +13224,21 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>43.6772</v>
+        <v>49.193901</v>
       </c>
       <c r="H341" t="n">
-        <v>-79.6306</v>
+        <v>-123.183998</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t>YVR</t>
+          <t>YWG</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Winnipeg, MB, Canada</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Winnipeg</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -13262,21 +13262,21 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>49.193901</v>
+        <v>49.91</v>
       </c>
       <c r="H342" t="n">
-        <v>-123.183998</v>
+        <v>-97.23989899999999</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t>YWG</t>
+          <t>CVG</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Winnipeg, MB, Canada</t>
+          <t>Cincinnati, United States</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -13286,61 +13286,23 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Winnipeg</t>
+          <t>Hebron</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>49.91</v>
+        <v>39.048801</v>
       </c>
       <c r="H343" t="n">
-        <v>-97.23989899999999</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="1" t="inlineStr">
-        <is>
-          <t>CVG</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Cincinnati, United States</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>Hebron</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G344" t="n">
-        <v>39.048801</v>
-      </c>
-      <c r="H344" t="n">
         <v>-84.667801</v>
       </c>
     </row>
